--- a/data/trans_camb/P1413-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1413-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,06</t>
+          <t>-3,86; 0,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; -1,65</t>
+          <t>-5,53; -1,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 6,28</t>
+          <t>-1,95; 6,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,86</t>
+          <t>-3,58; 1,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,17</t>
+          <t>-4,42; 0,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 11,89</t>
+          <t>0,09; 10,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,64</t>
+          <t>-2,77; 0,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -1,32</t>
+          <t>-4,4; -1,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 6,41</t>
+          <t>0,28; 6,3</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>110,7%</t>
+          <t>101,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,57; 49,59</t>
+          <t>-72,64; 37,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -44,56</t>
+          <t>-100,0; -45,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 191,25</t>
+          <t>-51,9; 214,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,12; 67,08</t>
+          <t>-59,03; 52,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,91; 5,23</t>
+          <t>-71,89; 20,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 317,58</t>
+          <t>-3,64; 276,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 20,28</t>
+          <t>-54,35; 25,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,43; -34,03</t>
+          <t>-82,21; -35,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 174,22</t>
+          <t>3,34; 182,37</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,29</t>
+          <t>-4,63; 0,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,5; -1,66</t>
+          <t>-6,57; -1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 4,29</t>
+          <t>-3,28; 4,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,61</t>
+          <t>-5,09; 1,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -0,9</t>
+          <t>-6,92; -1,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 4,91</t>
+          <t>-2,88; 5,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; -0,03</t>
+          <t>-4,04; 0,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -2,16</t>
+          <t>-5,94; -2,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,23</t>
+          <t>-1,74; 3,56</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>-0,06%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,7; 5,91</t>
+          <t>-56,17; 4,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-79,15; -25,64</t>
+          <t>-78,97; -29,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,86; 76,63</t>
+          <t>-40,96; 72,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 21,26</t>
+          <t>-45,3; 20,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,93; -10,13</t>
+          <t>-61,25; -10,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,15; 60,21</t>
+          <t>-25,72; 62,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,9; -0,45</t>
+          <t>-43,6; 2,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,32; -27,66</t>
+          <t>-63,33; -29,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 43,82</t>
+          <t>-18,98; 50,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,68</t>
+          <t>-3,96</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -4,9</t>
+          <t>-11,35; -4,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -4,45</t>
+          <t>-11,09; -4,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,2</t>
+          <t>-7,75; -0,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 2,72</t>
+          <t>-4,33; 3,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,76; -1,85</t>
+          <t>-8,88; -1,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 10,53</t>
+          <t>2,53; 10,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,07; -2,0</t>
+          <t>-7,04; -2,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -3,85</t>
+          <t>-8,87; -4,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,41</t>
+          <t>-1,15; 4,25</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-25,66%</t>
+          <t>-27,65%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,93; -38,22</t>
+          <t>-69,63; -38,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,65; -34,97</t>
+          <t>-66,9; -33,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,75; 2,54</t>
+          <t>-48,23; -2,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,79; 22,73</t>
+          <t>-27,8; 26,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,82; -14,63</t>
+          <t>-55,28; -14,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,43; 89,18</t>
+          <t>15,83; 87,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,23; -15,89</t>
+          <t>-45,34; -16,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,12; -30,42</t>
+          <t>-57,02; -30,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 34,37</t>
+          <t>-7,8; 32,69</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,42</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>3,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -6,12</t>
+          <t>-14,63; -6,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -5,74</t>
+          <t>-14,16; -6,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 2,64</t>
+          <t>-3,82; 5,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -0,29</t>
+          <t>-9,88; -0,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -5,17</t>
+          <t>-13,9; -5,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 9,2</t>
+          <t>1,06; 9,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -4,68</t>
+          <t>-10,92; -4,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,05; -6,8</t>
+          <t>-12,92; -6,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 4,34</t>
+          <t>0,18; 6,6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-22,86%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-3,4%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,65; -35,42</t>
+          <t>-66,59; -36,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,87; -34,72</t>
+          <t>-65,8; -36,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,09; 14,31</t>
+          <t>-17,51; 34,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,06; -0,11</t>
+          <t>-39,52; -2,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,5; -25,51</t>
+          <t>-54,11; -23,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 45,41</t>
+          <t>3,89; 49,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,04; -24,23</t>
+          <t>-47,73; -23,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,19; -35,03</t>
+          <t>-56,55; -35,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,89; 20,92</t>
+          <t>0,89; 34,27</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>-3,91</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>13,03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,96</t>
+          <t>4,6</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,4; -12,43</t>
+          <t>-24,08; -12,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-23,51; -12,36</t>
+          <t>-23,92; -12,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 2,44</t>
+          <t>-9,6; 1,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 6,25</t>
+          <t>-6,29; 5,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -0,46</t>
+          <t>-11,23; 0,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,66; 17,8</t>
+          <t>7,48; 18,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -5,14</t>
+          <t>-12,74; -4,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,63; -7,35</t>
+          <t>-15,63; -7,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,14</t>
+          <t>0,48; 8,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-9,92%</t>
+          <t>-12,89%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-70,89; -44,82</t>
+          <t>-70,64; -46,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-69,74; -44,59</t>
+          <t>-70,01; -43,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 9,31</t>
+          <t>-28,55; 7,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 27,14</t>
+          <t>-21,37; 25,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,93; -1,89</t>
+          <t>-38,45; 2,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,89; 78,56</t>
+          <t>24,71; 84,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,01; -18,7</t>
+          <t>-42,45; -17,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,62; -27,81</t>
+          <t>-51,08; -28,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,56; 35,01</t>
+          <t>1,58; 32,38</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,66</t>
+          <t>9,52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17,75</t>
+          <t>5,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,49; -0,66</t>
+          <t>-14,19; -1,16</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,99; -7,26</t>
+          <t>-19,86; -6,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 6,31</t>
+          <t>-6,01; 6,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 0,47</t>
+          <t>-13,18; 0,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-22,46; -9,71</t>
+          <t>-22,24; -9,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,55; 48,93</t>
+          <t>3,45; 15,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,61; -1,47</t>
+          <t>-11,88; -1,86</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-19,11; -10,28</t>
+          <t>-19,38; -10,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,25; 42,57</t>
+          <t>0,95; 9,8</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-48,67; -3,07</t>
+          <t>-47,58; -4,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-64,24; -31,72</t>
+          <t>-64,26; -27,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 27,78</t>
+          <t>-20,29; 29,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 1,26</t>
+          <t>-32,86; 2,32</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-55,27; -27,38</t>
+          <t>-55,21; -29,03</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,93; 154,38</t>
+          <t>8,04; 46,28</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,81; -4,96</t>
+          <t>-33,93; -5,74</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-55,86; -34,18</t>
+          <t>-55,45; -34,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9,81; 143,85</t>
+          <t>2,77; 33,68</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,19</t>
+          <t>21,95</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>14,71</t>
+          <t>15,25</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-21,64; -4,32</t>
+          <t>-21,02; -4,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-22,39; -7,05</t>
+          <t>-23,68; -6,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 12,04</t>
+          <t>-2,75; 12,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 10,22</t>
+          <t>-5,26; 10,33</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 2,21</t>
+          <t>-13,64; 1,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,64; 27,67</t>
+          <t>15,38; 28,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 2,36</t>
+          <t>-8,46; 2,77</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-15,6; -4,16</t>
+          <t>-15,07; -3,73</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,33; 19,41</t>
+          <t>10,16; 20,22</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>43,15%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,9; -13,82</t>
+          <t>-55,09; -15,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-57,39; -23,24</t>
+          <t>-59,32; -23,25</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 41,73</t>
+          <t>-6,84; 44,17</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 31,39</t>
+          <t>-12,47; 32,6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 7,19</t>
+          <t>-34,29; 5,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,16; 90,26</t>
+          <t>37,94; 90,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 7,25</t>
+          <t>-22,45; 8,8</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-40,2; -12,18</t>
+          <t>-38,83; -11,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>24,28; 61,54</t>
+          <t>26,38; 63,82</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,49</t>
+          <t>11,36</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,08</t>
+          <t>7,01</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -5,55</t>
+          <t>-8,84; -5,59</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,64; -6,39</t>
+          <t>-9,61; -6,57</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,4</t>
+          <t>0,52; 4,09</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,81</t>
+          <t>-3,05; 0,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -3,41</t>
+          <t>-7,09; -3,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,94; 26,69</t>
+          <t>9,58; 13,12</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -2,85</t>
+          <t>-5,29; -2,89</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,85; -5,49</t>
+          <t>-7,82; -5,41</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,97; 16,52</t>
+          <t>5,81; 8,32</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-51,11; -36,07</t>
+          <t>-52,04; -36,15</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-56,39; -41,7</t>
+          <t>-56,26; -42,0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 21,62</t>
+          <t>3,08; 26,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 4,43</t>
+          <t>-14,68; 4,46</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-34,69; -18,42</t>
+          <t>-35,43; -18,96</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>50,32; 142,82</t>
+          <t>46,85; 72,72</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-28,95; -16,5</t>
+          <t>-28,83; -16,82</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-42,67; -31,74</t>
+          <t>-42,67; -31,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>27,29; 92,86</t>
+          <t>31,45; 49,22</t>
         </is>
       </c>
     </row>
